--- a/files/港岛-西营盘及上环-42 Tung St..xlsx
+++ b/files/港岛-西营盘及上环-42 Tung St..xlsx
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>24238000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>41503</v>
+        <v>41432</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>24238000</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>41503</v>
+        <v>41432</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>18783000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>32163</v>
+        <v>32108</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>18783000</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>32163</v>
+        <v>32108</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>17412000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>29815</v>
+        <v>29764</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>17412000</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>29815</v>
+        <v>29764</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>17154000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>29373</v>
+        <v>29323</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>17154000</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>29373</v>
+        <v>29323</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>16574000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>28380</v>
+        <v>28332</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>16574000</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>28380</v>
+        <v>28332</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>16330000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>27962</v>
+        <v>27915</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>16330000</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>27962</v>
+        <v>27915</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>15932000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>27281</v>
+        <v>27234</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>15932000</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>27281</v>
+        <v>27234</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>15393000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>26358</v>
+        <v>26313</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>15393000</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>26358</v>
+        <v>26313</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>15393000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>26358</v>
+        <v>26313</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>15393000</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>26358</v>
+        <v>26313</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1703,9 +1703,9 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>- | 584呎 (2房)
+          <t>- | 585呎 (2房)
 $2424万
-$41,503/呎
+$41,432/呎
 (23年-09月-14日)</t>
         </is>
       </c>
@@ -1718,9 +1718,9 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>- | 584呎 (2房)
+          <t>- | 585呎 (2房)
 $1878万
-$32,163/呎
+$32,108/呎
 (26年-01月-27日)</t>
         </is>
       </c>
@@ -1733,9 +1733,9 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>- | 584呎 (2房)
+          <t>- | 585呎 (2房)
 $1741万
-$29,815/呎
+$29,764/呎
 (25年-10月-27日)</t>
         </is>
       </c>
@@ -1748,9 +1748,9 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>- | 584呎 (2房)
+          <t>- | 585呎 (2房)
 $1715万
-$29,373/呎
+$29,323/呎
 (26年-01月-12日)</t>
         </is>
       </c>
@@ -1763,9 +1763,9 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>- | 584呎 (2房)
+          <t>- | 585呎 (2房)
 $1657万
-$28,380/呎
+$28,332/呎
 (25年-12月-22日)</t>
         </is>
       </c>
@@ -1778,9 +1778,9 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>- | 584呎 (2房)
+          <t>- | 585呎 (2房)
 $1633万
-$27,962/呎
+$27,915/呎
 (24年-12月-05日)</t>
         </is>
       </c>
@@ -1793,9 +1793,9 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>- | 584呎 (2房)
+          <t>- | 585呎 (2房)
 $1593万
-$27,281/呎
+$27,234/呎
 (26年-01月-16日)</t>
         </is>
       </c>
@@ -1808,9 +1808,9 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>- | 584呎 (2房)
+          <t>- | 585呎 (2房)
 $1539万
-$26,358/呎
+$26,313/呎
 (25年-03月-28日)</t>
         </is>
       </c>
@@ -1823,9 +1823,9 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>- | 584呎 (2房)
+          <t>- | 585呎 (2房)
 $1539万
-$26,358/呎
+$26,313/呎
 (24年-12月-03日)</t>
         </is>
       </c>
